--- a/plan/smoke数据构造种子集.xlsx
+++ b/plan/smoke数据构造种子集.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11620"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$55</definedName>
@@ -30,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="131">
   <si>
     <t>一级目录</t>
   </si>
@@ -360,6 +362,69 @@
   </si>
   <si>
     <t>14.1.1 祈福、开光、活菩萨、财神等进行诱导宣传</t>
+  </si>
+  <si>
+    <t>姓名</t>
+  </si>
+  <si>
+    <t>UM</t>
+  </si>
+  <si>
+    <t>子项目名称</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>分组</t>
+  </si>
+  <si>
+    <t>转亚丽</t>
+  </si>
+  <si>
+    <t>萧梓健</t>
+  </si>
+  <si>
+    <t>XIAOZIJIAN556</t>
+  </si>
+  <si>
+    <t>AI 增员</t>
+  </si>
+  <si>
+    <t>分析组</t>
+  </si>
+  <si>
+    <t>金美芝</t>
+  </si>
+  <si>
+    <t>JINMEIZHI005</t>
+  </si>
+  <si>
+    <t>林俊鑫</t>
+  </si>
+  <si>
+    <t>LINJUNXIN113</t>
+  </si>
+  <si>
+    <t>AI 销售助手</t>
+  </si>
+  <si>
+    <t>阮智昊</t>
+  </si>
+  <si>
+    <t>RUANZHIHAO322</t>
+  </si>
+  <si>
+    <t>AI 学练考</t>
+  </si>
+  <si>
+    <t>尹俊琪</t>
+  </si>
+  <si>
+    <t>YINJUNQI509</t>
+  </si>
+  <si>
+    <t>智能合规</t>
   </si>
 </sst>
 </file>
@@ -372,13 +437,34 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color theme="1"/>
+      <name val=".applesystemuifont"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -734,7 +820,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -754,6 +840,21 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF9A9A9A"/>
       </bottom>
       <diagonal/>
     </border>
@@ -875,144 +976,162 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1549,607 +1668,607 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="8" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="8" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:3">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="8" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="8" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="8" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="8" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="8" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="8" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="8" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="8" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="8" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="8" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="8" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="8" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="8" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="2" t="s">
+      <c r="A53" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="8" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="8" t="s">
         <v>109</v>
       </c>
     </row>
@@ -2160,4 +2279,217 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="I12:K17"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="10" max="10" width="9.57142857142857"/>
+    <col min="11" max="11" width="12.7857142857143"/>
+  </cols>
+  <sheetData>
+    <row r="12" ht="17.55"/>
+    <row r="13" ht="17.55" spans="9:11">
+      <c r="I13" s="5">
+        <v>20790</v>
+      </c>
+      <c r="J13" s="5">
+        <v>15592.5</v>
+      </c>
+      <c r="K13">
+        <f>J13/I13</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="14" ht="17.55" spans="9:11">
+      <c r="I14" s="5">
+        <v>23100</v>
+      </c>
+      <c r="J14" s="5">
+        <v>18480</v>
+      </c>
+      <c r="K14">
+        <f>J14/I14</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" ht="17.55" spans="9:11">
+      <c r="I15" s="5">
+        <v>18570</v>
+      </c>
+      <c r="J15" s="5">
+        <v>13928</v>
+      </c>
+      <c r="K15">
+        <f>J15/I15</f>
+        <v>0.750026925148088</v>
+      </c>
+    </row>
+    <row r="16" ht="17.55" spans="9:11">
+      <c r="I16" s="5">
+        <v>23100</v>
+      </c>
+      <c r="J16" s="5">
+        <v>18480</v>
+      </c>
+      <c r="K16">
+        <f>J16/I16</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="9:11">
+      <c r="I17" s="6">
+        <v>15589</v>
+      </c>
+      <c r="J17">
+        <v>11691.5</v>
+      </c>
+      <c r="K17">
+        <f>J17/I17</f>
+        <v>0.749983963050869</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="H6:M11"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="9" max="9" width="14.1339285714286" customWidth="1"/>
+    <col min="10" max="10" width="13.0982142857143" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="8:13">
+      <c r="H6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="8:13">
+      <c r="H7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" s="3">
+        <v>23100</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M7" s="4">
+        <v>18480</v>
+      </c>
+    </row>
+    <row r="8" spans="8:13">
+      <c r="H8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K8" s="3">
+        <v>23100</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M8" s="4">
+        <v>18480</v>
+      </c>
+    </row>
+    <row r="9" spans="8:13">
+      <c r="H9" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K9" s="3">
+        <v>20790</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M9" s="4">
+        <v>15592.5</v>
+      </c>
+    </row>
+    <row r="10" spans="8:13">
+      <c r="H10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="K10" s="3">
+        <v>18570</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M10" s="4">
+        <v>13928</v>
+      </c>
+    </row>
+    <row r="11" spans="8:13">
+      <c r="H11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="K11" s="3">
+        <v>15589</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M11" s="4">
+        <v>11691.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>